--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6488-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6488-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C843393-5695-44A7-AADD-EC91B06403C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3A9B105-1985-4CC9-B616-223ED0197275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{16BB1593-F6DF-49E2-AB1C-DADE19ECB16F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E412E0C0-CB8B-4783-9D57-4D3C998B0307}"/>
   </bookViews>
   <sheets>
     <sheet name="6488-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1490,23 +1490,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF88AAA8-AF38-4042-B5F0-10B9AB5E8B88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA007326-3CE3-4991-973F-F1DA9726E1A9}">
   <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1533,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1564,7 +1563,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1610,7 +1609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1660,7 +1659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1714,7 +1713,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1770,7 +1769,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="39">
         <v>2024</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1992,7 +1991,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2048,7 +2047,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2023</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2214,7 +2213,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2022</v>
       </c>
@@ -2268,7 +2267,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2324,7 +2323,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2021</v>
       </c>
@@ -2434,7 +2433,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2490,7 +2489,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2020</v>
       </c>
@@ -2600,7 +2599,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2019</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2018</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2017</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2016</v>
       </c>
@@ -2816,7 +2815,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2015</v>
       </c>
@@ -2870,7 +2869,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
         <v>49</v>
       </c>
